--- a/consolidated.xlsx
+++ b/consolidated.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,12 @@
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -62,12 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,19 +440,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="39" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -509,17 +516,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pywin32</t>
+          <t>numpy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PSF</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -549,34 +556,34 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/pywin32</t>
+          <t>https://pypi.org/project/numpy</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Python for Window Extensions</t>
+          <t>Fundamental package for array computing in Python</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>xlwings</t>
+          <t>pandas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.33.20</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BSD 3-clause</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -591,12 +598,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pywin32==311</t>
+          <t>numpy==2.4.1, python-dateutil==2.9.0.post0, tzdata==2025.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>six==1.17.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -611,12 +618,354 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://pypi.org/project/xlwings</t>
+          <t>https://pypi.org/project/pandas</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Make Excel fly: Interact with Excel from Python and vice versa.</t>
+          <t>Powerful data structures for data analysis, time series, and statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pyodbc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5.3.0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sin problemas detectados</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/mkleehammer/pyodbc</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>DB API module for ODBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>python-dateutil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.9.0.post0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apache</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sin problemas detectados</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>six==1.17.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/dateutil/dateutil</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Extensions to the standard Python datetime module</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pywin32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PSF</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sin problemas detectados</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/pywin32</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Python for Window Extensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>six</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.17.0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sin problemas detectados</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/benjaminp/six</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Python 2 and 3 compatibility utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tzdata</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025.3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sin problemas detectados</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://github.com/python/tzdata</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Provider of IANA time zone data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>unidecode</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.4.0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GPL</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Licencia rechazada por política</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://pypi.org/project/unidecode</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ASCII transliterations of Unicode text</t>
         </is>
       </c>
     </row>
